--- a/output/full_scan/batch_seq0_2026-05-23.xlsx
+++ b/output/full_scan/batch_seq0_2026-05-23.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP302"/>
+  <dimension ref="A1:CP324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86832,6 +86832,6294 @@
       <c r="CO302" t="inlineStr"/>
       <c r="CP302" t="inlineStr"/>
     </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="C303" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="D303" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="E303" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F303" t="n">
+        <v>1997455</v>
+      </c>
+      <c r="G303" t="n">
+        <v>115340594</v>
+      </c>
+      <c r="H303" t="n">
+        <v>5258</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>虹堡</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr"/>
+      <c r="K303" t="n">
+        <v>2.466096806103621</v>
+      </c>
+      <c r="L303" t="n">
+        <v>1.88305575553308</v>
+      </c>
+      <c r="M303" t="n">
+        <v>0.5830410505705415</v>
+      </c>
+      <c r="N303" t="n">
+        <v>53.95224412191065</v>
+      </c>
+      <c r="O303" t="n">
+        <v>52.71943624480207</v>
+      </c>
+      <c r="P303" t="n">
+        <v>56.21486609229484</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>62.27262127208873</v>
+      </c>
+      <c r="R303" t="n">
+        <v>35.42937927452282</v>
+      </c>
+      <c r="S303" t="n">
+        <v>3.288926131173329</v>
+      </c>
+      <c r="T303" t="n">
+        <v>1893942.1</v>
+      </c>
+      <c r="U303" t="n">
+        <v>104949131</v>
+      </c>
+      <c r="V303" t="n">
+        <v>60</v>
+      </c>
+      <c r="W303" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="X303" t="n">
+        <v>1.326877980250058</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>0.2334233793039111</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>0.07663551401869161</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>0.0069930069930068</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>1.518649447025361</v>
+      </c>
+      <c r="AD303" t="n">
+        <v>61.32910587954599</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>52.53249999999989</v>
+      </c>
+      <c r="AF303" t="n">
+        <v>43.73589412045379</v>
+      </c>
+      <c r="AG303" t="n">
+        <v>0.7880372310292473</v>
+      </c>
+      <c r="AH303" t="n">
+        <v>0.3349014754502876</v>
+      </c>
+      <c r="AI303" t="n">
+        <v>58.77862595419848</v>
+      </c>
+      <c r="AJ303" t="n">
+        <v>59.68094129536379</v>
+      </c>
+      <c r="AK303" t="n">
+        <v>3520738</v>
+      </c>
+      <c r="AL303" t="n">
+        <v>2177457.1</v>
+      </c>
+      <c r="AM303" t="n">
+        <v>-34.50479233226837</v>
+      </c>
+      <c r="AN303" t="n">
+        <v>84.20181968569061</v>
+      </c>
+      <c r="AO303" t="n">
+        <v>63.67695598618206</v>
+      </c>
+      <c r="AP303" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="AQ303" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AR303" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS303" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT303" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU303" t="n">
+        <v>257768</v>
+      </c>
+      <c r="AV303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY303" t="n">
+        <v>-236</v>
+      </c>
+      <c r="AZ303" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA303" t="n">
+        <v>0.0500235027026407</v>
+      </c>
+      <c r="BB303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD303" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF303" t="n">
+        <v>1.054654733109317</v>
+      </c>
+      <c r="BG303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH303" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI303" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL303" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN303" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP303" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV303" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW303" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX303" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY303" t="b">
+        <v>1</v>
+      </c>
+      <c r="BZ303" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA303" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB303" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC303" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD303" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE303" t="n">
+        <v>9</v>
+      </c>
+      <c r="CF303" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG303" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH303" t="n">
+        <v>1020.97827687588</v>
+      </c>
+      <c r="CI303" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="CJ303" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK303" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL303" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM303" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN303" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO303" t="inlineStr">
+        <is>
+          <t>long_upper_shadow</t>
+        </is>
+      </c>
+      <c r="CP303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C304" t="n">
+        <v>1495</v>
+      </c>
+      <c r="D304" t="n">
+        <v>1420</v>
+      </c>
+      <c r="E304" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F304" t="n">
+        <v>1861941</v>
+      </c>
+      <c r="G304" t="n">
+        <v>2715422015</v>
+      </c>
+      <c r="H304" t="n">
+        <v>5269</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="n">
+        <v>48.72427493437817</v>
+      </c>
+      <c r="L304" t="n">
+        <v>51.16349202166885</v>
+      </c>
+      <c r="M304" t="n">
+        <v>-2.439217087290672</v>
+      </c>
+      <c r="N304" t="n">
+        <v>1381.205378037156</v>
+      </c>
+      <c r="O304" t="n">
+        <v>1307.299257794532</v>
+      </c>
+      <c r="P304" t="n">
+        <v>1322.704213004859</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>61.72862529587379</v>
+      </c>
+      <c r="R304" t="n">
+        <v>29.67064265778687</v>
+      </c>
+      <c r="S304" t="n">
+        <v>79.0136749451994</v>
+      </c>
+      <c r="T304" t="n">
+        <v>2547657.7</v>
+      </c>
+      <c r="U304" t="n">
+        <v>3580985678</v>
+      </c>
+      <c r="V304" t="n">
+        <v>1525</v>
+      </c>
+      <c r="W304" t="n">
+        <v>1380</v>
+      </c>
+      <c r="X304" t="n">
+        <v>0.5844929508842013</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>0.2931098780691418</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>0.0171821305841923</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>0.0496453900709219</v>
+      </c>
+      <c r="AB304" t="n">
+        <v>1410</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>0.7925894626095228</v>
+      </c>
+      <c r="AD304" t="n">
+        <v>1513.096587752666</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>1385.25</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>1257.403412247334</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>0.8705613175351429</v>
+      </c>
+      <c r="AH304" t="n">
+        <v>0.1845826930195495</v>
+      </c>
+      <c r="AI304" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="AJ304" t="n">
+        <v>52.46913580246898</v>
+      </c>
+      <c r="AK304" t="n">
+        <v>-10076359</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>-12072094.4</v>
+      </c>
+      <c r="AM304" t="n">
+        <v>-24.07407407407408</v>
+      </c>
+      <c r="AN304" t="n">
+        <v>110.7506687154974</v>
+      </c>
+      <c r="AO304" t="n">
+        <v>46.70207498642364</v>
+      </c>
+      <c r="AP304" t="n">
+        <v>1140</v>
+      </c>
+      <c r="AQ304" t="n">
+        <v>1237.5</v>
+      </c>
+      <c r="AR304" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS304" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT304" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU304" t="n">
+        <v>214892</v>
+      </c>
+      <c r="AV304" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW304" t="n">
+        <v>143000</v>
+      </c>
+      <c r="AX304" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY304" t="n">
+        <v>60042</v>
+      </c>
+      <c r="AZ304" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA304" t="n">
+        <v>-0.0094298807318584</v>
+      </c>
+      <c r="BB304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD304" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF304" t="n">
+        <v>0.7308442574526397</v>
+      </c>
+      <c r="BG304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH304" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI304" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK304" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL304" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP304" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ304" t="b">
+        <v>1</v>
+      </c>
+      <c r="BR304" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV304" t="b">
+        <v>1</v>
+      </c>
+      <c r="BW304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BX304" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY304" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ304" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA304" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB304" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC304" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD304" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE304" t="n">
+        <v>11</v>
+      </c>
+      <c r="CF304" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG304" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH304" t="n">
+        <v>1251.036097159127</v>
+      </c>
+      <c r="CI304" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="CJ304" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK304" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL304" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM304" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN304" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, cci_momentum, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO304" t="inlineStr"/>
+      <c r="CP304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>81</v>
+      </c>
+      <c r="C305" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="D305" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="E305" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="F305" t="n">
+        <v>5906546</v>
+      </c>
+      <c r="G305" t="n">
+        <v>472002037</v>
+      </c>
+      <c r="H305" t="n">
+        <v>5285</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>界霖</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr"/>
+      <c r="K305" t="n">
+        <v>7.150403050268778</v>
+      </c>
+      <c r="L305" t="n">
+        <v>5.741922969507117</v>
+      </c>
+      <c r="M305" t="n">
+        <v>1.408480080761661</v>
+      </c>
+      <c r="N305" t="n">
+        <v>68.58857949474891</v>
+      </c>
+      <c r="O305" t="n">
+        <v>59.02677518695627</v>
+      </c>
+      <c r="P305" t="n">
+        <v>55.07478412777752</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>77.2768481078522</v>
+      </c>
+      <c r="R305" t="n">
+        <v>52.61374993305543</v>
+      </c>
+      <c r="S305" t="n">
+        <v>3.766871048433241</v>
+      </c>
+      <c r="T305" t="n">
+        <v>2267090.1</v>
+      </c>
+      <c r="U305" t="n">
+        <v>169956141.45</v>
+      </c>
+      <c r="V305" t="n">
+        <v>82</v>
+      </c>
+      <c r="W305" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="X305" t="n">
+        <v>2.6531959347019</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>0.7750912547830026</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>0.06603773584905639</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>-0.0353658536585366</v>
+      </c>
+      <c r="AB305" t="n">
+        <v>82</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>4.324218865499958</v>
+      </c>
+      <c r="AD305" t="n">
+        <v>86.54059522961722</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>65.64499999999998</v>
+      </c>
+      <c r="AF305" t="n">
+        <v>44.74940477038274</v>
+      </c>
+      <c r="AG305" t="n">
+        <v>0.8219578062301142</v>
+      </c>
+      <c r="AH305" t="n">
+        <v>0.636624121551291</v>
+      </c>
+      <c r="AI305" t="n">
+        <v>55.8620689655172</v>
+      </c>
+      <c r="AJ305" t="n">
+        <v>79.42153121749227</v>
+      </c>
+      <c r="AK305" t="n">
+        <v>35827463</v>
+      </c>
+      <c r="AL305" t="n">
+        <v>20432852.9</v>
+      </c>
+      <c r="AM305" t="n">
+        <v>-20.98360655737707</v>
+      </c>
+      <c r="AN305" t="n">
+        <v>94.29632129598367</v>
+      </c>
+      <c r="AO305" t="n">
+        <v>80.34266785329669</v>
+      </c>
+      <c r="AP305" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="AQ305" t="n">
+        <v>51.775</v>
+      </c>
+      <c r="AR305" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS305" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT305" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU305" t="n">
+        <v>-180743</v>
+      </c>
+      <c r="AV305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY305" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AZ305" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA305" t="n">
+        <v>0.0394257245330056</v>
+      </c>
+      <c r="BB305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD305" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE305" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF305" t="n">
+        <v>2.605342416695305</v>
+      </c>
+      <c r="BG305" t="b">
+        <v>1</v>
+      </c>
+      <c r="BH305" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI305" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL305" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN305" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP305" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW305" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX305" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY305" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ305" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA305" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB305" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC305" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD305" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE305" t="n">
+        <v>11</v>
+      </c>
+      <c r="CF305" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG305" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH305" t="n">
+        <v>1252.609746553309</v>
+      </c>
+      <c r="CI305" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="CJ305" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK305" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL305" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM305" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN305" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO305" t="inlineStr"/>
+      <c r="CP305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="C306" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="D306" t="n">
+        <v>219</v>
+      </c>
+      <c r="E306" t="n">
+        <v>219.5</v>
+      </c>
+      <c r="F306" t="n">
+        <v>98116</v>
+      </c>
+      <c r="G306" t="n">
+        <v>21671906</v>
+      </c>
+      <c r="H306" t="n">
+        <v>5292</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>華懋</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr"/>
+      <c r="K306" t="n">
+        <v>-2.064657377654498</v>
+      </c>
+      <c r="L306" t="n">
+        <v>0.3044443290601833</v>
+      </c>
+      <c r="M306" t="n">
+        <v>-2.369101706714682</v>
+      </c>
+      <c r="N306" t="n">
+        <v>227.4027618451312</v>
+      </c>
+      <c r="O306" t="n">
+        <v>217.8817095740102</v>
+      </c>
+      <c r="P306" t="n">
+        <v>200.8643165888517</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>44.37521637955236</v>
+      </c>
+      <c r="R306" t="n">
+        <v>19.81648436048929</v>
+      </c>
+      <c r="S306" t="n">
+        <v>9.800609474624755</v>
+      </c>
+      <c r="T306" t="n">
+        <v>339632.15</v>
+      </c>
+      <c r="U306" t="n">
+        <v>79660260.05</v>
+      </c>
+      <c r="V306" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="W306" t="n">
+        <v>219</v>
+      </c>
+      <c r="X306" t="n">
+        <v>-0.6667513394646463</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>0.5193384827741605</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>-0.0330396475770925</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>-0.0045351473922902</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>0.2918097813885467</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>251.1474048927952</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>231.4</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>211.6525951072048</v>
+      </c>
+      <c r="AG306" t="n">
+        <v>0.1986945863367167</v>
+      </c>
+      <c r="AH306" t="n">
+        <v>0.1706776568089473</v>
+      </c>
+      <c r="AI306" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="AJ306" t="n">
+        <v>37.81702898550733</v>
+      </c>
+      <c r="AK306" t="n">
+        <v>4435369</v>
+      </c>
+      <c r="AL306" t="n">
+        <v>5572750.5</v>
+      </c>
+      <c r="AM306" t="n">
+        <v>-66.66666666666667</v>
+      </c>
+      <c r="AN306" t="n">
+        <v>-87.95411089866171</v>
+      </c>
+      <c r="AO306" t="n">
+        <v>29.88451271034937</v>
+      </c>
+      <c r="AP306" t="n">
+        <v>222.125</v>
+      </c>
+      <c r="AQ306" t="n">
+        <v>214.75</v>
+      </c>
+      <c r="AR306" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS306" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT306" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU306" t="n">
+        <v>-8983</v>
+      </c>
+      <c r="AV306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ306" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA306" t="n">
+        <v>-0.0596516588931433</v>
+      </c>
+      <c r="BB306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD306" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE306" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF306" t="n">
+        <v>0.288889023020936</v>
+      </c>
+      <c r="BG306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK306" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL306" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BX306" t="b">
+        <v>0</v>
+      </c>
+      <c r="BY306" t="b">
+        <v>1</v>
+      </c>
+      <c r="BZ306" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA306" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB306" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC306" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD306" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE306" t="n">
+        <v>5</v>
+      </c>
+      <c r="CF306" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG306" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH306" t="n">
+        <v>516.7402087013843</v>
+      </c>
+      <c r="CI306" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="CJ306" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK306" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL306" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM306" t="b">
+        <v>1</v>
+      </c>
+      <c r="CN306" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+      <c r="CO306" t="inlineStr">
+        <is>
+          <t>long_upper_shadow</t>
+        </is>
+      </c>
+      <c r="CP306" t="inlineStr">
+        <is>
+          <t>close_below_ema20</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="C307" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="D307" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="E307" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="F307" t="n">
+        <v>5975457</v>
+      </c>
+      <c r="G307" t="n">
+        <v>507944526</v>
+      </c>
+      <c r="H307" t="n">
+        <v>5388</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>中磊</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr"/>
+      <c r="K307" t="n">
+        <v>0.4788554074551712</v>
+      </c>
+      <c r="L307" t="n">
+        <v>0.1560594426870809</v>
+      </c>
+      <c r="M307" t="n">
+        <v>0.3227959647680902</v>
+      </c>
+      <c r="N307" t="n">
+        <v>81.09165035173895</v>
+      </c>
+      <c r="O307" t="n">
+        <v>80.95009963755491</v>
+      </c>
+      <c r="P307" t="n">
+        <v>83.12853080278201</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>58.84563937033886</v>
+      </c>
+      <c r="R307" t="n">
+        <v>16.98691093769559</v>
+      </c>
+      <c r="S307" t="n">
+        <v>3.176010029055492</v>
+      </c>
+      <c r="T307" t="n">
+        <v>6804597.3</v>
+      </c>
+      <c r="U307" t="n">
+        <v>552398519.4</v>
+      </c>
+      <c r="V307" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="W307" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="X307" t="n">
+        <v>0.3247835271125458</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>0.0440498138030598</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>0.09664948453608251</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>0.0253012048192771</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>83</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>0.6542273872967522</v>
+      </c>
+      <c r="AD307" t="n">
+        <v>87.26748888294047</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>80.23999999999997</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>73.21251111705946</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>0.8457849653663532</v>
+      </c>
+      <c r="AH307" t="n">
+        <v>0.1751617368629238</v>
+      </c>
+      <c r="AI307" t="n">
+        <v>68.4615384615384</v>
+      </c>
+      <c r="AJ307" t="n">
+        <v>54.61538461538476</v>
+      </c>
+      <c r="AK307" t="n">
+        <v>39032471</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>16946502.45</v>
+      </c>
+      <c r="AM307" t="n">
+        <v>-31.5384615384616</v>
+      </c>
+      <c r="AN307" t="n">
+        <v>113.8881731512498</v>
+      </c>
+      <c r="AO307" t="n">
+        <v>73.21703496801481</v>
+      </c>
+      <c r="AP307" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="AQ307" t="n">
+        <v>81.95</v>
+      </c>
+      <c r="AR307" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS307" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT307" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU307" t="n">
+        <v>3228122</v>
+      </c>
+      <c r="AV307" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW307" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="AX307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY307" t="n">
+        <v>64123</v>
+      </c>
+      <c r="AZ307" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA307" t="n">
+        <v>0.0700374732200317</v>
+      </c>
+      <c r="BB307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD307" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF307" t="n">
+        <v>0.8781499825125582</v>
+      </c>
+      <c r="BG307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH307" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL307" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM307" t="b">
+        <v>1</v>
+      </c>
+      <c r="BN307" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP307" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV307" t="b">
+        <v>1</v>
+      </c>
+      <c r="BW307" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX307" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY307" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ307" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA307" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB307" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC307" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD307" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE307" t="n">
+        <v>10</v>
+      </c>
+      <c r="CF307" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG307" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH307" t="n">
+        <v>1132.772158084824</v>
+      </c>
+      <c r="CI307" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="CJ307" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK307" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL307" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM307" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN307" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO307" t="inlineStr"/>
+      <c r="CP307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>424</v>
+      </c>
+      <c r="C308" t="n">
+        <v>454.5</v>
+      </c>
+      <c r="D308" t="n">
+        <v>422</v>
+      </c>
+      <c r="E308" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="F308" t="n">
+        <v>2028959</v>
+      </c>
+      <c r="G308" t="n">
+        <v>889743548</v>
+      </c>
+      <c r="H308" t="n">
+        <v>5434</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr"/>
+      <c r="K308" t="n">
+        <v>8.59339327320572</v>
+      </c>
+      <c r="L308" t="n">
+        <v>9.680949619826375</v>
+      </c>
+      <c r="M308" t="n">
+        <v>-1.087556346620655</v>
+      </c>
+      <c r="N308" t="n">
+        <v>411.2268788675885</v>
+      </c>
+      <c r="O308" t="n">
+        <v>381.9075593033844</v>
+      </c>
+      <c r="P308" t="n">
+        <v>355.1501344698536</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>67.75756794754406</v>
+      </c>
+      <c r="R308" t="n">
+        <v>25.60271133448282</v>
+      </c>
+      <c r="S308" t="n">
+        <v>15.10971640935056</v>
+      </c>
+      <c r="T308" t="n">
+        <v>783883.6</v>
+      </c>
+      <c r="U308" t="n">
+        <v>327027588.55</v>
+      </c>
+      <c r="V308" t="n">
+        <v>431</v>
+      </c>
+      <c r="W308" t="n">
+        <v>394</v>
+      </c>
+      <c r="X308" t="n">
+        <v>0.0297452767777133</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>0.5771067511530474</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>0.07279236276849629</v>
+      </c>
+      <c r="AB308" t="n">
+        <v>419</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>1.033211773707773</v>
+      </c>
+      <c r="AD308" t="n">
+        <v>439.0445662710154</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>414.375</v>
+      </c>
+      <c r="AF308" t="n">
+        <v>389.7054337289845</v>
+      </c>
+      <c r="AG308" t="n">
+        <v>1.211909557187244</v>
+      </c>
+      <c r="AH308" t="n">
+        <v>0.1190687964815226</v>
+      </c>
+      <c r="AI308" t="n">
+        <v>92.1875</v>
+      </c>
+      <c r="AJ308" t="n">
+        <v>55.29057017543831</v>
+      </c>
+      <c r="AK308" t="n">
+        <v>28790730</v>
+      </c>
+      <c r="AL308" t="n">
+        <v>27158133.45</v>
+      </c>
+      <c r="AM308" t="n">
+        <v>-7.8125</v>
+      </c>
+      <c r="AN308" t="n">
+        <v>219.9933132731522</v>
+      </c>
+      <c r="AO308" t="n">
+        <v>58.69593621021613</v>
+      </c>
+      <c r="AP308" t="n">
+        <v>360.875</v>
+      </c>
+      <c r="AQ308" t="n">
+        <v>358</v>
+      </c>
+      <c r="AR308" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS308" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT308" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU308" t="n">
+        <v>379664</v>
+      </c>
+      <c r="AV308" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW308" t="n">
+        <v>-7000</v>
+      </c>
+      <c r="AX308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY308" t="n">
+        <v>55056</v>
+      </c>
+      <c r="AZ308" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA308" t="n">
+        <v>0.08877260406856451</v>
+      </c>
+      <c r="BB308" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC308" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF308" t="n">
+        <v>2.588342197744665</v>
+      </c>
+      <c r="BG308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BH308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BK308" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BN308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO308" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ308" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BT308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BU308" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BW308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX308" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY308" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ308" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA308" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB308" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC308" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD308" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE308" t="n">
+        <v>17</v>
+      </c>
+      <c r="CF308" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG308" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH308" t="n">
+        <v>1940.363393718786</v>
+      </c>
+      <c r="CI308" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="CJ308" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK308" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL308" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM308" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN308" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO308" t="inlineStr"/>
+      <c r="CP308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="C309" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="D309" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="E309" t="n">
+        <v>54</v>
+      </c>
+      <c r="F309" t="n">
+        <v>4079111</v>
+      </c>
+      <c r="G309" t="n">
+        <v>217703162</v>
+      </c>
+      <c r="H309" t="n">
+        <v>5471</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>松翰</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr"/>
+      <c r="K309" t="n">
+        <v>2.798959074986101</v>
+      </c>
+      <c r="L309" t="n">
+        <v>2.325246314221889</v>
+      </c>
+      <c r="M309" t="n">
+        <v>0.473712760764212</v>
+      </c>
+      <c r="N309" t="n">
+        <v>48.2229545378009</v>
+      </c>
+      <c r="O309" t="n">
+        <v>43.75798199231686</v>
+      </c>
+      <c r="P309" t="n">
+        <v>40.8628182693568</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>67.98249606400606</v>
+      </c>
+      <c r="R309" t="n">
+        <v>38.01676208776644</v>
+      </c>
+      <c r="S309" t="n">
+        <v>2.498390114386805</v>
+      </c>
+      <c r="T309" t="n">
+        <v>3300831.05</v>
+      </c>
+      <c r="U309" t="n">
+        <v>163568696</v>
+      </c>
+      <c r="V309" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="W309" t="n">
+        <v>45.35</v>
+      </c>
+      <c r="X309" t="n">
+        <v>1.340954177636035</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>0.2902958786871615</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>0.062992125984252</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>0.0285714285714284</v>
+      </c>
+      <c r="AB309" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>1.928122340488506</v>
+      </c>
+      <c r="AD309" t="n">
+        <v>55.57019788283333</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>47.29499999999989</v>
+      </c>
+      <c r="AF309" t="n">
+        <v>39.01980211716645</v>
+      </c>
+      <c r="AG309" t="n">
+        <v>0.905126263742246</v>
+      </c>
+      <c r="AH309" t="n">
+        <v>0.3499396503999771</v>
+      </c>
+      <c r="AI309" t="n">
+        <v>98.46153846153844</v>
+      </c>
+      <c r="AJ309" t="n">
+        <v>89.59339875678172</v>
+      </c>
+      <c r="AK309" t="n">
+        <v>65597209</v>
+      </c>
+      <c r="AL309" t="n">
+        <v>43569077.85</v>
+      </c>
+      <c r="AM309" t="n">
+        <v>-0.9090909090909221</v>
+      </c>
+      <c r="AN309" t="n">
+        <v>112.1432908318154</v>
+      </c>
+      <c r="AO309" t="n">
+        <v>79.90657039428686</v>
+      </c>
+      <c r="AP309" t="n">
+        <v>40.025</v>
+      </c>
+      <c r="AQ309" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR309" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS309" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT309" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU309" t="n">
+        <v>1093260</v>
+      </c>
+      <c r="AV309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY309" t="n">
+        <v>1580</v>
+      </c>
+      <c r="AZ309" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA309" t="n">
+        <v>0.0363801146682012</v>
+      </c>
+      <c r="BB309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD309" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE309" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF309" t="n">
+        <v>1.235783031064253</v>
+      </c>
+      <c r="BG309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH309" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI309" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ309" t="b">
+        <v>1</v>
+      </c>
+      <c r="BK309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL309" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN309" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP309" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW309" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX309" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY309" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ309" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA309" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB309" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC309" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD309" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE309" t="n">
+        <v>11</v>
+      </c>
+      <c r="CF309" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG309" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH309" t="n">
+        <v>1224.012603865229</v>
+      </c>
+      <c r="CI309" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="CJ309" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK309" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL309" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM309" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN309" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO309" t="inlineStr"/>
+      <c r="CP309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>43</v>
+      </c>
+      <c r="C310" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="D310" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="E310" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="F310" t="n">
+        <v>2154100</v>
+      </c>
+      <c r="G310" t="n">
+        <v>95570811</v>
+      </c>
+      <c r="H310" t="n">
+        <v>5484</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>慧友</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr"/>
+      <c r="K310" t="n">
+        <v>0.6778884776981045</v>
+      </c>
+      <c r="L310" t="n">
+        <v>0.0864823608773127</v>
+      </c>
+      <c r="M310" t="n">
+        <v>0.5914061168207917</v>
+      </c>
+      <c r="N310" t="n">
+        <v>39.97387487688061</v>
+      </c>
+      <c r="O310" t="n">
+        <v>39.61003032446581</v>
+      </c>
+      <c r="P310" t="n">
+        <v>39.54150733475536</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>66.68728016554029</v>
+      </c>
+      <c r="R310" t="n">
+        <v>22.83833792714239</v>
+      </c>
+      <c r="S310" t="n">
+        <v>2.231284378031186</v>
+      </c>
+      <c r="T310" t="n">
+        <v>709218.9</v>
+      </c>
+      <c r="U310" t="n">
+        <v>28750361.55</v>
+      </c>
+      <c r="V310" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="W310" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="X310" t="n">
+        <v>0.5984208918929981</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>0.050112325605281</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>0.1009852216748767</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>0.065554231227652</v>
+      </c>
+      <c r="AB310" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>2.043967382745829</v>
+      </c>
+      <c r="AD310" t="n">
+        <v>42.80946155144167</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>39.16500000000024</v>
+      </c>
+      <c r="AF310" t="n">
+        <v>35.5205384485588</v>
+      </c>
+      <c r="AG310" t="n">
+        <v>1.259371435515708</v>
+      </c>
+      <c r="AH310" t="n">
+        <v>0.1861080838218516</v>
+      </c>
+      <c r="AI310" t="n">
+        <v>92.1052631578948</v>
+      </c>
+      <c r="AJ310" t="n">
+        <v>64.70411566105334</v>
+      </c>
+      <c r="AK310" t="n">
+        <v>8289590</v>
+      </c>
+      <c r="AL310" t="n">
+        <v>2951224.1</v>
+      </c>
+      <c r="AM310" t="n">
+        <v>-7.792207792207723</v>
+      </c>
+      <c r="AN310" t="n">
+        <v>274.1145177096461</v>
+      </c>
+      <c r="AO310" t="n">
+        <v>74.65067002077056</v>
+      </c>
+      <c r="AP310" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="AQ310" t="n">
+        <v>40.125</v>
+      </c>
+      <c r="AR310" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS310" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT310" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU310" t="n">
+        <v>46100</v>
+      </c>
+      <c r="AV310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW310" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="AX310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY310" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="AZ310" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA310" t="n">
+        <v>0.07437321035882589</v>
+      </c>
+      <c r="BB310" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC310" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF310" t="n">
+        <v>3.037285103372175</v>
+      </c>
+      <c r="BG310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BH310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BK310" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL310" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM310" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO310" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ310" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR310" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BT310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BU310" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV310" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX310" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY310" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ310" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA310" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB310" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC310" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD310" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE310" t="n">
+        <v>13</v>
+      </c>
+      <c r="CF310" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG310" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH310" t="n">
+        <v>1480.648509996747</v>
+      </c>
+      <c r="CI310" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="CJ310" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK310" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL310" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM310" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN310" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO310" t="inlineStr"/>
+      <c r="CP310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="C311" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="D311" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="E311" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="F311" t="n">
+        <v>2093159</v>
+      </c>
+      <c r="G311" t="n">
+        <v>173802291</v>
+      </c>
+      <c r="H311" t="n">
+        <v>5469</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>瀚宇博</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr"/>
+      <c r="K311" t="n">
+        <v>-2.032405672937941</v>
+      </c>
+      <c r="L311" t="n">
+        <v>-1.953439573733114</v>
+      </c>
+      <c r="M311" t="n">
+        <v>-0.0789660992048264</v>
+      </c>
+      <c r="N311" t="n">
+        <v>83.14726047558307</v>
+      </c>
+      <c r="O311" t="n">
+        <v>86.76707336468318</v>
+      </c>
+      <c r="P311" t="n">
+        <v>87.66520406579988</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>47.40779027519411</v>
+      </c>
+      <c r="R311" t="n">
+        <v>25.56939737070275</v>
+      </c>
+      <c r="S311" t="n">
+        <v>3.115407313770133</v>
+      </c>
+      <c r="T311" t="n">
+        <v>3613595.65</v>
+      </c>
+      <c r="U311" t="n">
+        <v>303022979.9</v>
+      </c>
+      <c r="V311" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="W311" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="X311" t="n">
+        <v>-0.6027230531929086</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>-0.1417172969221951</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>0.0414572864321609</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>0.0159313725490197</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>0.6820911456047271</v>
+      </c>
+      <c r="AD311" t="n">
+        <v>90.94570947099184</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>83.47499999999999</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>76.00429052900816</v>
+      </c>
+      <c r="AG311" t="n">
+        <v>0.4615163725592149</v>
+      </c>
+      <c r="AH311" t="n">
+        <v>0.1789927396464051</v>
+      </c>
+      <c r="AI311" t="n">
+        <v>67.03296703296706</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>47.70664118490155</v>
+      </c>
+      <c r="AK311" t="n">
+        <v>153580260</v>
+      </c>
+      <c r="AL311" t="n">
+        <v>158338183.1</v>
+      </c>
+      <c r="AM311" t="n">
+        <v>-33.69565217391297</v>
+      </c>
+      <c r="AN311" t="n">
+        <v>-17.77125621586354</v>
+      </c>
+      <c r="AO311" t="n">
+        <v>43.55918742488007</v>
+      </c>
+      <c r="AP311" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="AQ311" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AR311" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS311" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT311" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU311" t="n">
+        <v>440550</v>
+      </c>
+      <c r="AV311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY311" t="n">
+        <v>6999</v>
+      </c>
+      <c r="AZ311" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA311" t="n">
+        <v>0.0148452751161101</v>
+      </c>
+      <c r="BB311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF311" t="n">
+        <v>0.5792454947193663</v>
+      </c>
+      <c r="BG311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI311" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK311" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL311" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN311" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR311" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BX311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BY311" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ311" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA311" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB311" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC311" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD311" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE311" t="n">
+        <v>6</v>
+      </c>
+      <c r="CF311" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG311" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH311" t="n">
+        <v>672.8463798295073</v>
+      </c>
+      <c r="CI311" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="CJ311" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK311" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL311" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM311" t="b">
+        <v>1</v>
+      </c>
+      <c r="CN311" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
+        </is>
+      </c>
+      <c r="CO311" t="inlineStr"/>
+      <c r="CP311" t="inlineStr">
+        <is>
+          <t>close_below_ema20</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>19</v>
+      </c>
+      <c r="C312" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="D312" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E312" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="F312" t="n">
+        <v>1492845</v>
+      </c>
+      <c r="G312" t="n">
+        <v>28704668</v>
+      </c>
+      <c r="H312" t="n">
+        <v>6108</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>競國</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr"/>
+      <c r="K312" t="n">
+        <v>0.2827626305666655</v>
+      </c>
+      <c r="L312" t="n">
+        <v>0.5464892532630348</v>
+      </c>
+      <c r="M312" t="n">
+        <v>-0.2637266226963692</v>
+      </c>
+      <c r="N312" t="n">
+        <v>19.27535617825222</v>
+      </c>
+      <c r="O312" t="n">
+        <v>17.9146915430292</v>
+      </c>
+      <c r="P312" t="n">
+        <v>16.71938914353663</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>52.48679022422661</v>
+      </c>
+      <c r="R312" t="n">
+        <v>25.22461154005794</v>
+      </c>
+      <c r="S312" t="n">
+        <v>1.025476726024235</v>
+      </c>
+      <c r="T312" t="n">
+        <v>3900186.2</v>
+      </c>
+      <c r="U312" t="n">
+        <v>80700866.40000001</v>
+      </c>
+      <c r="V312" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="W312" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="X312" t="n">
+        <v>-0.3166043531829818</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>0.5315465831611812</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>0.0456989247311827</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>0.0103896103896103</v>
+      </c>
+      <c r="AB312" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="AC312" t="n">
+        <v>0.2215108485178843</v>
+      </c>
+      <c r="AD312" t="n">
+        <v>22.57513272989581</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>19.86749999999997</v>
+      </c>
+      <c r="AF312" t="n">
+        <v>17.15986727010413</v>
+      </c>
+      <c r="AG312" t="n">
+        <v>0.4229031331704959</v>
+      </c>
+      <c r="AH312" t="n">
+        <v>0.2725690428987887</v>
+      </c>
+      <c r="AI312" t="n">
+        <v>52.83018867924526</v>
+      </c>
+      <c r="AJ312" t="n">
+        <v>38.93281421583318</v>
+      </c>
+      <c r="AK312" t="n">
+        <v>34286231</v>
+      </c>
+      <c r="AL312" t="n">
+        <v>32475808.9</v>
+      </c>
+      <c r="AM312" t="n">
+        <v>-77.23577235772359</v>
+      </c>
+      <c r="AN312" t="n">
+        <v>-38.81193061275437</v>
+      </c>
+      <c r="AO312" t="n">
+        <v>62.01937742075845</v>
+      </c>
+      <c r="AP312" t="n">
+        <v>16.575</v>
+      </c>
+      <c r="AQ312" t="n">
+        <v>15.925</v>
+      </c>
+      <c r="AR312" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS312" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT312" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU312" t="n">
+        <v>357000</v>
+      </c>
+      <c r="AV312" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY312" t="n">
+        <v>-25396</v>
+      </c>
+      <c r="AZ312" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA312" t="n">
+        <v>0.0190869134151319</v>
+      </c>
+      <c r="BB312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD312" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE312" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF312" t="n">
+        <v>0.3827624947752494</v>
+      </c>
+      <c r="BG312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI312" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK312" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL312" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN312" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP312" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW312" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX312" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY312" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ312" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA312" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB312" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC312" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD312" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE312" t="n">
+        <v>10</v>
+      </c>
+      <c r="CF312" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG312" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH312" t="n">
+        <v>1100.960927829324</v>
+      </c>
+      <c r="CI312" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="CJ312" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK312" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL312" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM312" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN312" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO312" t="inlineStr"/>
+      <c r="CP312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="C313" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="D313" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="E313" t="n">
+        <v>46.95</v>
+      </c>
+      <c r="F313" t="n">
+        <v>142540</v>
+      </c>
+      <c r="G313" t="n">
+        <v>6683680</v>
+      </c>
+      <c r="H313" t="n">
+        <v>6115</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>鎰勝</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr"/>
+      <c r="K313" t="n">
+        <v>-0.1594618924258881</v>
+      </c>
+      <c r="L313" t="n">
+        <v>-0.0712096543595125</v>
+      </c>
+      <c r="M313" t="n">
+        <v>-0.0882522380663756</v>
+      </c>
+      <c r="N313" t="n">
+        <v>47.23317616514879</v>
+      </c>
+      <c r="O313" t="n">
+        <v>47.25973401462687</v>
+      </c>
+      <c r="P313" t="n">
+        <v>47.34506792246505</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>42.19063856340242</v>
+      </c>
+      <c r="R313" t="n">
+        <v>17.34245146671823</v>
+      </c>
+      <c r="S313" t="n">
+        <v>0.4128703418057111</v>
+      </c>
+      <c r="T313" t="n">
+        <v>184804.05</v>
+      </c>
+      <c r="U313" t="n">
+        <v>8769611</v>
+      </c>
+      <c r="V313" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="W313" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="X313" t="n">
+        <v>-0.1403143168710429</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>0.0128482155458562</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>0.0053533190578158</v>
+      </c>
+      <c r="AA313" t="n">
+        <v>-0.0010638297872339</v>
+      </c>
+      <c r="AB313" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC313" t="n">
+        <v>0.3617519911780532</v>
+      </c>
+      <c r="AD313" t="n">
+        <v>48.31741712328948</v>
+      </c>
+      <c r="AE313" t="n">
+        <v>47.41249999999991</v>
+      </c>
+      <c r="AF313" t="n">
+        <v>46.50758287671034</v>
+      </c>
+      <c r="AG313" t="n">
+        <v>0.244451735912225</v>
+      </c>
+      <c r="AH313" t="n">
+        <v>0.0381720906212316</v>
+      </c>
+      <c r="AI313" t="n">
+        <v>42.3076923076925</v>
+      </c>
+      <c r="AJ313" t="n">
+        <v>36.95970695970694</v>
+      </c>
+      <c r="AK313" t="n">
+        <v>-3028126</v>
+      </c>
+      <c r="AL313" t="n">
+        <v>-2376012.5</v>
+      </c>
+      <c r="AM313" t="n">
+        <v>-68.57142857142833</v>
+      </c>
+      <c r="AN313" t="n">
+        <v>-83.68084514873622</v>
+      </c>
+      <c r="AO313" t="n">
+        <v>52.62417759813473</v>
+      </c>
+      <c r="AP313" t="n">
+        <v>47</v>
+      </c>
+      <c r="AQ313" t="n">
+        <v>47.075</v>
+      </c>
+      <c r="AR313" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS313" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT313" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU313" t="n">
+        <v>-78000</v>
+      </c>
+      <c r="AV313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY313" t="n">
+        <v>-358</v>
+      </c>
+      <c r="AZ313" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA313" t="n">
+        <v>-0.0212586922582349</v>
+      </c>
+      <c r="BB313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF313" t="n">
+        <v>0.7713034427546367</v>
+      </c>
+      <c r="BG313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK313" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW313" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BY313" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ313" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA313" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB313" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC313" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD313" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE313" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF313" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG313" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH313" t="n">
+        <v>332.929616668441</v>
+      </c>
+      <c r="CI313" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="CJ313" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK313" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL313" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM313" t="b">
+        <v>1</v>
+      </c>
+      <c r="CN313" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+      <c r="CO313" t="inlineStr"/>
+      <c r="CP313" t="inlineStr">
+        <is>
+          <t>close_below_ema20</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="C314" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="D314" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="E314" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="F314" t="n">
+        <v>548635</v>
+      </c>
+      <c r="G314" t="n">
+        <v>23527197</v>
+      </c>
+      <c r="H314" t="n">
+        <v>6112</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>邁達特</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr"/>
+      <c r="K314" t="n">
+        <v>-1.05118118035022</v>
+      </c>
+      <c r="L314" t="n">
+        <v>-0.8736582743243141</v>
+      </c>
+      <c r="M314" t="n">
+        <v>-0.1775229060259057</v>
+      </c>
+      <c r="N314" t="n">
+        <v>43.78585606960733</v>
+      </c>
+      <c r="O314" t="n">
+        <v>45.17860242602983</v>
+      </c>
+      <c r="P314" t="n">
+        <v>46.34785908466446</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>42.77750774746029</v>
+      </c>
+      <c r="R314" t="n">
+        <v>17.00029565337597</v>
+      </c>
+      <c r="S314" t="n">
+        <v>1.266522135453827</v>
+      </c>
+      <c r="T314" t="n">
+        <v>565286.5</v>
+      </c>
+      <c r="U314" t="n">
+        <v>24991134.7</v>
+      </c>
+      <c r="V314" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="W314" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="X314" t="n">
+        <v>-0.5692962597802529</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>-0.1066252134952578</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>0.0274463007159904</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>0.0153301886792451</v>
+      </c>
+      <c r="AB314" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AC314" t="n">
+        <v>0.7707362677505086</v>
+      </c>
+      <c r="AD314" t="n">
+        <v>47.86389283636687</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>44.14999999999991</v>
+      </c>
+      <c r="AF314" t="n">
+        <v>40.43610716363294</v>
+      </c>
+      <c r="AG314" t="n">
+        <v>0.3519074124556647</v>
+      </c>
+      <c r="AH314" t="n">
+        <v>0.1682397660868391</v>
+      </c>
+      <c r="AI314" t="n">
+        <v>62.12121212121209</v>
+      </c>
+      <c r="AJ314" t="n">
+        <v>40.58022081277886</v>
+      </c>
+      <c r="AK314" t="n">
+        <v>-19775553</v>
+      </c>
+      <c r="AL314" t="n">
+        <v>-17314594.05</v>
+      </c>
+      <c r="AM314" t="n">
+        <v>-72.6666666666667</v>
+      </c>
+      <c r="AN314" t="n">
+        <v>-51.00292309243049</v>
+      </c>
+      <c r="AO314" t="n">
+        <v>32.42308076450321</v>
+      </c>
+      <c r="AP314" t="n">
+        <v>45.975</v>
+      </c>
+      <c r="AQ314" t="n">
+        <v>46.375</v>
+      </c>
+      <c r="AR314" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS314" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT314" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU314" t="n">
+        <v>89000</v>
+      </c>
+      <c r="AV314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY314" t="n">
+        <v>-46294</v>
+      </c>
+      <c r="AZ314" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA314" t="n">
+        <v>0.0008342893999395</v>
+      </c>
+      <c r="BB314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF314" t="n">
+        <v>0.9705432554996448</v>
+      </c>
+      <c r="BG314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK314" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN314" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BX314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BY314" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ314" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA314" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB314" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC314" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD314" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE314" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF314" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG314" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH314" t="n">
+        <v>336.7891571483664</v>
+      </c>
+      <c r="CI314" t="n">
+        <v>12</v>
+      </c>
+      <c r="CJ314" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK314" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL314" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM314" t="b">
+        <v>1</v>
+      </c>
+      <c r="CN314" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+        </is>
+      </c>
+      <c r="CO314" t="inlineStr"/>
+      <c r="CP314" t="inlineStr">
+        <is>
+          <t>close_below_ema20</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C315" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="D315" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="E315" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="F315" t="n">
+        <v>101107069</v>
+      </c>
+      <c r="G315" t="n">
+        <v>1186348668</v>
+      </c>
+      <c r="H315" t="n">
+        <v>6116</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>彩晶</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr"/>
+      <c r="K315" t="n">
+        <v>0.6053998971565235</v>
+      </c>
+      <c r="L315" t="n">
+        <v>0.4334122123385669</v>
+      </c>
+      <c r="M315" t="n">
+        <v>0.1719876848179566</v>
+      </c>
+      <c r="N315" t="n">
+        <v>9.879357469320739</v>
+      </c>
+      <c r="O315" t="n">
+        <v>9.149353871248024</v>
+      </c>
+      <c r="P315" t="n">
+        <v>8.728864348259137</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>71.02638751923888</v>
+      </c>
+      <c r="R315" t="n">
+        <v>35.56102068319223</v>
+      </c>
+      <c r="S315" t="n">
+        <v>0.6326232521189115</v>
+      </c>
+      <c r="T315" t="n">
+        <v>80107191.34999999</v>
+      </c>
+      <c r="U315" t="n">
+        <v>841727012.35</v>
+      </c>
+      <c r="V315" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="W315" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="X315" t="n">
+        <v>1.83614359940066</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>0.2408046891715779</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>0.1560975609756096</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>0.0972222222222221</v>
+      </c>
+      <c r="AB315" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AC315" t="n">
+        <v>1.136155938187272</v>
+      </c>
+      <c r="AD315" t="n">
+        <v>11.78718327446179</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>9.520000000000016</v>
+      </c>
+      <c r="AF315" t="n">
+        <v>7.252816725538238</v>
+      </c>
+      <c r="AG315" t="n">
+        <v>1.013853473216258</v>
+      </c>
+      <c r="AH315" t="n">
+        <v>0.4762990072398684</v>
+      </c>
+      <c r="AI315" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ315" t="n">
+        <v>63.94657149037448</v>
+      </c>
+      <c r="AK315" t="n">
+        <v>1188733455</v>
+      </c>
+      <c r="AL315" t="n">
+        <v>806898330.8</v>
+      </c>
+      <c r="AM315" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN315" t="n">
+        <v>140.1050396692367</v>
+      </c>
+      <c r="AO315" t="n">
+        <v>74.93197231151103</v>
+      </c>
+      <c r="AP315" t="n">
+        <v>8.7575</v>
+      </c>
+      <c r="AQ315" t="n">
+        <v>9.275</v>
+      </c>
+      <c r="AR315" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS315" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT315" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU315" t="n">
+        <v>24560767</v>
+      </c>
+      <c r="AV315" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY315" t="n">
+        <v>745989</v>
+      </c>
+      <c r="AZ315" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA315" t="n">
+        <v>0.1294855496595588</v>
+      </c>
+      <c r="BB315" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC315" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF315" t="n">
+        <v>1.2621472216926</v>
+      </c>
+      <c r="BG315" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BK315" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM315" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO315" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ315" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS315" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT315" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU315" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BW315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX315" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY315" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ315" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA315" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB315" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC315" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD315" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE315" t="n">
+        <v>13</v>
+      </c>
+      <c r="CF315" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG315" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH315" t="n">
+        <v>1461.131047866074</v>
+      </c>
+      <c r="CI315" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="CJ315" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK315" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL315" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM315" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN315" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO315" t="inlineStr"/>
+      <c r="CP315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="C316" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="D316" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="E316" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="F316" t="n">
+        <v>1400142</v>
+      </c>
+      <c r="G316" t="n">
+        <v>120504601</v>
+      </c>
+      <c r="H316" t="n">
+        <v>6117</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>迎廣</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr"/>
+      <c r="K316" t="n">
+        <v>0.6895992304854275</v>
+      </c>
+      <c r="L316" t="n">
+        <v>0.848650082554405</v>
+      </c>
+      <c r="M316" t="n">
+        <v>-0.1590508520689775</v>
+      </c>
+      <c r="N316" t="n">
+        <v>82.35481784113792</v>
+      </c>
+      <c r="O316" t="n">
+        <v>80.00540810179231</v>
+      </c>
+      <c r="P316" t="n">
+        <v>79.91575252151253</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>62.44624491797941</v>
+      </c>
+      <c r="R316" t="n">
+        <v>19.76149663077392</v>
+      </c>
+      <c r="S316" t="n">
+        <v>3.385188505881651</v>
+      </c>
+      <c r="T316" t="n">
+        <v>1117517.45</v>
+      </c>
+      <c r="U316" t="n">
+        <v>96226256.95</v>
+      </c>
+      <c r="V316" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="W316" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="X316" t="n">
+        <v>-0.4858473663935959</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>0.3603271256525664</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>0.0779537149817297</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="AB316" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="AC316" t="n">
+        <v>0.6149986153907016</v>
+      </c>
+      <c r="AD316" t="n">
+        <v>91.70387776812612</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>84.02999999999993</v>
+      </c>
+      <c r="AF316" t="n">
+        <v>76.35612223187373</v>
+      </c>
+      <c r="AG316" t="n">
+        <v>0.7912477977279242</v>
+      </c>
+      <c r="AH316" t="n">
+        <v>0.1826461446656244</v>
+      </c>
+      <c r="AI316" t="n">
+        <v>99.05660377358495</v>
+      </c>
+      <c r="AJ316" t="n">
+        <v>64.68135748175457</v>
+      </c>
+      <c r="AK316" t="n">
+        <v>46723021</v>
+      </c>
+      <c r="AL316" t="n">
+        <v>46790415.45</v>
+      </c>
+      <c r="AM316" t="n">
+        <v>-4.545454545454546</v>
+      </c>
+      <c r="AN316" t="n">
+        <v>47.19736222326913</v>
+      </c>
+      <c r="AO316" t="n">
+        <v>40.63540525765376</v>
+      </c>
+      <c r="AP316" t="n">
+        <v>74.69999999999999</v>
+      </c>
+      <c r="AQ316" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AR316" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS316" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT316" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU316" t="n">
+        <v>541000</v>
+      </c>
+      <c r="AV316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY316" t="n">
+        <v>37000</v>
+      </c>
+      <c r="AZ316" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA316" t="n">
+        <v>0.0513417036656789</v>
+      </c>
+      <c r="BB316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD316" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE316" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF316" t="n">
+        <v>1.252903925571811</v>
+      </c>
+      <c r="BG316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH316" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL316" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN316" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BX316" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY316" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ316" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA316" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB316" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC316" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD316" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE316" t="n">
+        <v>7</v>
+      </c>
+      <c r="CF316" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG316" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH316" t="n">
+        <v>767.4247062530599</v>
+      </c>
+      <c r="CI316" t="n">
+        <v>26</v>
+      </c>
+      <c r="CJ316" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK316" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL316" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM316" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN316" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO316" t="inlineStr"/>
+      <c r="CP316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C317" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D317" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E317" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F317" t="n">
+        <v>13984511</v>
+      </c>
+      <c r="G317" t="n">
+        <v>202973457</v>
+      </c>
+      <c r="H317" t="n">
+        <v>6120</v>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>達運</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr"/>
+      <c r="K317" t="n">
+        <v>-0.0221645973668316</v>
+      </c>
+      <c r="L317" t="n">
+        <v>-0.152608052825178</v>
+      </c>
+      <c r="M317" t="n">
+        <v>0.1304434554583464</v>
+      </c>
+      <c r="N317" t="n">
+        <v>13.25760742027481</v>
+      </c>
+      <c r="O317" t="n">
+        <v>13.24402776450482</v>
+      </c>
+      <c r="P317" t="n">
+        <v>12.90952179121286</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>65.57815576875859</v>
+      </c>
+      <c r="R317" t="n">
+        <v>13.11818373735263</v>
+      </c>
+      <c r="S317" t="n">
+        <v>0.6512103120711608</v>
+      </c>
+      <c r="T317" t="n">
+        <v>3835241.5</v>
+      </c>
+      <c r="U317" t="n">
+        <v>50925065.65</v>
+      </c>
+      <c r="V317" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="W317" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="X317" t="n">
+        <v>0.0877937659875295</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>0.0141405925645264</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>0.09701492537313421</v>
+      </c>
+      <c r="AB317" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AC317" t="n">
+        <v>1.6842357689339</v>
+      </c>
+      <c r="AD317" t="n">
+        <v>13.96561090377242</v>
+      </c>
+      <c r="AE317" t="n">
+        <v>13.06500000000001</v>
+      </c>
+      <c r="AF317" t="n">
+        <v>12.1643890962276</v>
+      </c>
+      <c r="AG317" t="n">
+        <v>1.40771719127063</v>
+      </c>
+      <c r="AH317" t="n">
+        <v>0.1378661926938246</v>
+      </c>
+      <c r="AI317" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ317" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AK317" t="n">
+        <v>118768688</v>
+      </c>
+      <c r="AL317" t="n">
+        <v>102006825.75</v>
+      </c>
+      <c r="AM317" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN317" t="n">
+        <v>336.1227336122752</v>
+      </c>
+      <c r="AO317" t="n">
+        <v>69.75720523764682</v>
+      </c>
+      <c r="AP317" t="n">
+        <v>13.875</v>
+      </c>
+      <c r="AQ317" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AR317" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS317" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT317" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU317" t="n">
+        <v>6592760</v>
+      </c>
+      <c r="AV317" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW317" t="n">
+        <v>84000</v>
+      </c>
+      <c r="AX317" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY317" t="n">
+        <v>519783</v>
+      </c>
+      <c r="AZ317" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA317" t="n">
+        <v>0.1400546553506159</v>
+      </c>
+      <c r="BB317" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC317" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF317" t="n">
+        <v>3.64631823054689</v>
+      </c>
+      <c r="BG317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BH317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI317" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BK317" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BN317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO317" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BR317" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BT317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BU317" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BW317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX317" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY317" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ317" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA317" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB317" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC317" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD317" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE317" t="n">
+        <v>16</v>
+      </c>
+      <c r="CF317" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG317" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH317" t="n">
+        <v>1848.586831577883</v>
+      </c>
+      <c r="CI317" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="CJ317" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK317" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL317" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM317" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN317" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO317" t="inlineStr"/>
+      <c r="CP317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>24</v>
+      </c>
+      <c r="C318" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="D318" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E318" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F318" t="n">
+        <v>2771330</v>
+      </c>
+      <c r="G318" t="n">
+        <v>66499641</v>
+      </c>
+      <c r="H318" t="n">
+        <v>6133</v>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>金橋</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr"/>
+      <c r="K318" t="n">
+        <v>0.1331011835465538</v>
+      </c>
+      <c r="L318" t="n">
+        <v>-0.1825613498803475</v>
+      </c>
+      <c r="M318" t="n">
+        <v>0.3156625334269014</v>
+      </c>
+      <c r="N318" t="n">
+        <v>22.59416602580929</v>
+      </c>
+      <c r="O318" t="n">
+        <v>22.6568125621494</v>
+      </c>
+      <c r="P318" t="n">
+        <v>21.82031763653869</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>60.5603661989443</v>
+      </c>
+      <c r="R318" t="n">
+        <v>12.12654814370055</v>
+      </c>
+      <c r="S318" t="n">
+        <v>0.9899337550387892</v>
+      </c>
+      <c r="T318" t="n">
+        <v>1813882.45</v>
+      </c>
+      <c r="U318" t="n">
+        <v>41931261.6</v>
+      </c>
+      <c r="V318" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="W318" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="X318" t="n">
+        <v>0.3074573964755623</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>-0.2197762386934294</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>0.1476190476190477</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>0.0041666666666666</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>2.423612894891404</v>
+      </c>
+      <c r="AD318" t="n">
+        <v>24.13902716804128</v>
+      </c>
+      <c r="AE318" t="n">
+        <v>22.225</v>
+      </c>
+      <c r="AF318" t="n">
+        <v>20.31097283195873</v>
+      </c>
+      <c r="AG318" t="n">
+        <v>0.989804959748504</v>
+      </c>
+      <c r="AH318" t="n">
+        <v>0.1722409150093386</v>
+      </c>
+      <c r="AI318" t="n">
+        <v>86.20689655172418</v>
+      </c>
+      <c r="AJ318" t="n">
+        <v>88.45101258894404</v>
+      </c>
+      <c r="AK318" t="n">
+        <v>113123480</v>
+      </c>
+      <c r="AL318" t="n">
+        <v>104771249.4</v>
+      </c>
+      <c r="AM318" t="n">
+        <v>-13.79310344827582</v>
+      </c>
+      <c r="AN318" t="n">
+        <v>178.5198402583049</v>
+      </c>
+      <c r="AO318" t="n">
+        <v>57.94033430666515</v>
+      </c>
+      <c r="AP318" t="n">
+        <v>23.9875</v>
+      </c>
+      <c r="AQ318" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="AR318" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS318" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT318" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU318" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AV318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ318" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA318" t="n">
+        <v>0.1210070363029969</v>
+      </c>
+      <c r="BB318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD318" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE318" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF318" t="n">
+        <v>1.527844320893011</v>
+      </c>
+      <c r="BG318" t="b">
+        <v>1</v>
+      </c>
+      <c r="BH318" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN318" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP318" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW318" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BY318" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ318" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA318" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB318" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC318" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD318" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE318" t="n">
+        <v>8</v>
+      </c>
+      <c r="CF318" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG318" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH318" t="n">
+        <v>874.5056949829303</v>
+      </c>
+      <c r="CI318" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="CJ318" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK318" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL318" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM318" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN318" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+      <c r="CO318" t="inlineStr"/>
+      <c r="CP318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="C319" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="D319" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E319" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F319" t="n">
+        <v>377247</v>
+      </c>
+      <c r="G319" t="n">
+        <v>7107211</v>
+      </c>
+      <c r="H319" t="n">
+        <v>6128</v>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>上福</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="n">
+        <v>-0.601117283923255</v>
+      </c>
+      <c r="L319" t="n">
+        <v>-0.506240016010775</v>
+      </c>
+      <c r="M319" t="n">
+        <v>-0.09487726791248</v>
+      </c>
+      <c r="N319" t="n">
+        <v>19.87161583190396</v>
+      </c>
+      <c r="O319" t="n">
+        <v>21.16523854065663</v>
+      </c>
+      <c r="P319" t="n">
+        <v>22.67586904219697</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>29.64413074593791</v>
+      </c>
+      <c r="R319" t="n">
+        <v>28.55620988870711</v>
+      </c>
+      <c r="S319" t="n">
+        <v>0.3971415862532879</v>
+      </c>
+      <c r="T319" t="n">
+        <v>155590.85</v>
+      </c>
+      <c r="U319" t="n">
+        <v>3098046.2</v>
+      </c>
+      <c r="V319" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="W319" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X319" t="n">
+        <v>-0.5455058990336736</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>-0.4323356449870408</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>-0.0284237726098192</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>-0.0208333333333332</v>
+      </c>
+      <c r="AB319" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AC319" t="n">
+        <v>1.294592193914032</v>
+      </c>
+      <c r="AD319" t="n">
+        <v>21.43442158912621</v>
+      </c>
+      <c r="AE319" t="n">
+        <v>20.03000000000002</v>
+      </c>
+      <c r="AF319" t="n">
+        <v>18.62557841087382</v>
+      </c>
+      <c r="AG319" t="n">
+        <v>0.0620973041416637</v>
+      </c>
+      <c r="AH319" t="n">
+        <v>0.1402318111958255</v>
+      </c>
+      <c r="AI319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ319" t="n">
+        <v>7.619047619047706</v>
+      </c>
+      <c r="AK319" t="n">
+        <v>-9242586</v>
+      </c>
+      <c r="AL319" t="n">
+        <v>-8510114.449999999</v>
+      </c>
+      <c r="AM319" t="n">
+        <v>-100</v>
+      </c>
+      <c r="AN319" t="n">
+        <v>-131.646755680487</v>
+      </c>
+      <c r="AO319" t="n">
+        <v>30.68535828455378</v>
+      </c>
+      <c r="AP319" t="n">
+        <v>21.6625</v>
+      </c>
+      <c r="AQ319" t="n">
+        <v>23.925</v>
+      </c>
+      <c r="AR319" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS319" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT319" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU319" t="n">
+        <v>36000</v>
+      </c>
+      <c r="AV319" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY319" t="n">
+        <v>-295</v>
+      </c>
+      <c r="AZ319" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA319" t="n">
+        <v>-0.05503578392587</v>
+      </c>
+      <c r="BB319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF319" t="n">
+        <v>2.424609159214697</v>
+      </c>
+      <c r="BG319" t="b">
+        <v>1</v>
+      </c>
+      <c r="BH319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI319" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK319" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BX319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BY319" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ319" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA319" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB319" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC319" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD319" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE319" t="n">
+        <v>4</v>
+      </c>
+      <c r="CF319" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG319" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH319" t="n">
+        <v>462.298723088267</v>
+      </c>
+      <c r="CI319" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="CJ319" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK319" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL319" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM319" t="b">
+        <v>1</v>
+      </c>
+      <c r="CN319" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+      <c r="CO319" t="inlineStr"/>
+      <c r="CP319" t="inlineStr">
+        <is>
+          <t>close_below_ema20</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="C320" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D320" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="E320" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="F320" t="n">
+        <v>568045</v>
+      </c>
+      <c r="G320" t="n">
+        <v>14485152</v>
+      </c>
+      <c r="H320" t="n">
+        <v>6136</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>富爾特</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="n">
+        <v>0.0492732336010881</v>
+      </c>
+      <c r="L320" t="n">
+        <v>0.0607885246583408</v>
+      </c>
+      <c r="M320" t="n">
+        <v>-0.0115152910572526</v>
+      </c>
+      <c r="N320" t="n">
+        <v>25.22067846291198</v>
+      </c>
+      <c r="O320" t="n">
+        <v>24.85930958733829</v>
+      </c>
+      <c r="P320" t="n">
+        <v>24.47930461007507</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>56.03377802514607</v>
+      </c>
+      <c r="R320" t="n">
+        <v>15.05956115026762</v>
+      </c>
+      <c r="S320" t="n">
+        <v>0.6912435090640938</v>
+      </c>
+      <c r="T320" t="n">
+        <v>733963</v>
+      </c>
+      <c r="U320" t="n">
+        <v>19119666.75</v>
+      </c>
+      <c r="V320" t="n">
+        <v>28</v>
+      </c>
+      <c r="W320" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="X320" t="n">
+        <v>-0.2186406837013886</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>0.1431755196808857</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>0.0362173038229376</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>0.0117878192534381</v>
+      </c>
+      <c r="AB320" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="AC320" t="n">
+        <v>0.4282715054257472</v>
+      </c>
+      <c r="AD320" t="n">
+        <v>26.81361641018301</v>
+      </c>
+      <c r="AE320" t="n">
+        <v>25.35749999999998</v>
+      </c>
+      <c r="AF320" t="n">
+        <v>23.90138358981695</v>
+      </c>
+      <c r="AG320" t="n">
+        <v>0.6347763122698012</v>
+      </c>
+      <c r="AH320" t="n">
+        <v>0.114847000704567</v>
+      </c>
+      <c r="AI320" t="n">
+        <v>96.1538461538461</v>
+      </c>
+      <c r="AJ320" t="n">
+        <v>64.37451437451455</v>
+      </c>
+      <c r="AK320" t="n">
+        <v>6976634</v>
+      </c>
+      <c r="AL320" t="n">
+        <v>6934038.45</v>
+      </c>
+      <c r="AM320" t="n">
+        <v>-23.52941176470581</v>
+      </c>
+      <c r="AN320" t="n">
+        <v>15.53004726536152</v>
+      </c>
+      <c r="AO320" t="n">
+        <v>52.18075905069001</v>
+      </c>
+      <c r="AP320" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AQ320" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="AR320" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS320" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT320" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU320" t="n">
+        <v>21000</v>
+      </c>
+      <c r="AV320" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ320" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA320" t="n">
+        <v>0.009605292506886701</v>
+      </c>
+      <c r="BB320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD320" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE320" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF320" t="n">
+        <v>0.773942283194112</v>
+      </c>
+      <c r="BG320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH320" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK320" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM320" t="b">
+        <v>1</v>
+      </c>
+      <c r="BN320" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP320" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW320" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX320" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY320" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ320" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA320" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB320" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC320" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD320" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE320" t="n">
+        <v>10</v>
+      </c>
+      <c r="CF320" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG320" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH320" t="n">
+        <v>1108.759513232898</v>
+      </c>
+      <c r="CI320" t="n">
+        <v>13</v>
+      </c>
+      <c r="CJ320" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK320" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL320" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM320" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN320" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO320" t="inlineStr"/>
+      <c r="CP320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>808</v>
+      </c>
+      <c r="C321" t="n">
+        <v>808</v>
+      </c>
+      <c r="D321" t="n">
+        <v>767</v>
+      </c>
+      <c r="E321" t="n">
+        <v>769</v>
+      </c>
+      <c r="F321" t="n">
+        <v>6471356</v>
+      </c>
+      <c r="G321" t="n">
+        <v>5075673886</v>
+      </c>
+      <c r="H321" t="n">
+        <v>6139</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="n">
+        <v>28.59967006801605</v>
+      </c>
+      <c r="L321" t="n">
+        <v>24.85475648934434</v>
+      </c>
+      <c r="M321" t="n">
+        <v>3.744913578671706</v>
+      </c>
+      <c r="N321" t="n">
+        <v>709.3366174910659</v>
+      </c>
+      <c r="O321" t="n">
+        <v>647.3601972080713</v>
+      </c>
+      <c r="P321" t="n">
+        <v>585.4079340341264</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>62.98820292714004</v>
+      </c>
+      <c r="R321" t="n">
+        <v>22.58192627934615</v>
+      </c>
+      <c r="S321" t="n">
+        <v>43.54291217768997</v>
+      </c>
+      <c r="T321" t="n">
+        <v>4764499.7</v>
+      </c>
+      <c r="U321" t="n">
+        <v>3406764543.3</v>
+      </c>
+      <c r="V321" t="n">
+        <v>784</v>
+      </c>
+      <c r="W321" t="n">
+        <v>679</v>
+      </c>
+      <c r="X321" t="n">
+        <v>0.5359104021561616</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>0.6387549563000577</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>0.1096681096681095</v>
+      </c>
+      <c r="AA321" t="n">
+        <v>-0.0191326530612244</v>
+      </c>
+      <c r="AB321" t="n">
+        <v>784</v>
+      </c>
+      <c r="AC321" t="n">
+        <v>1.642641087392265</v>
+      </c>
+      <c r="AD321" t="n">
+        <v>767.8869841048119</v>
+      </c>
+      <c r="AE321" t="n">
+        <v>705.95</v>
+      </c>
+      <c r="AF321" t="n">
+        <v>644.0130158951882</v>
+      </c>
+      <c r="AG321" t="n">
+        <v>1.008985066929516</v>
+      </c>
+      <c r="AH321" t="n">
+        <v>0.1754713056301772</v>
+      </c>
+      <c r="AI321" t="n">
+        <v>73.10344827586206</v>
+      </c>
+      <c r="AJ321" t="n">
+        <v>75.39370924174061</v>
+      </c>
+      <c r="AK321" t="n">
+        <v>395043675</v>
+      </c>
+      <c r="AL321" t="n">
+        <v>388239662.85</v>
+      </c>
+      <c r="AM321" t="n">
+        <v>-25.49019607843137</v>
+      </c>
+      <c r="AN321" t="n">
+        <v>213.5289323553378</v>
+      </c>
+      <c r="AO321" t="n">
+        <v>60.18119326130424</v>
+      </c>
+      <c r="AP321" t="n">
+        <v>581.125</v>
+      </c>
+      <c r="AQ321" t="n">
+        <v>574.75</v>
+      </c>
+      <c r="AR321" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS321" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT321" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU321" t="n">
+        <v>-2102139</v>
+      </c>
+      <c r="AV321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW321" t="n">
+        <v>1043000</v>
+      </c>
+      <c r="AX321" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY321" t="n">
+        <v>-121487</v>
+      </c>
+      <c r="AZ321" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA321" t="n">
+        <v>0.0830560983520587</v>
+      </c>
+      <c r="BB321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD321" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE321" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF321" t="n">
+        <v>1.358244602261178</v>
+      </c>
+      <c r="BG321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH321" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI321" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL321" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN321" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP321" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ321" t="b">
+        <v>1</v>
+      </c>
+      <c r="BR321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS321" t="b">
+        <v>1</v>
+      </c>
+      <c r="BT321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW321" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX321" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY321" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ321" t="b">
+        <v>1</v>
+      </c>
+      <c r="CA321" t="b">
+        <v>1</v>
+      </c>
+      <c r="CB321" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC321" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD321" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE321" t="n">
+        <v>12</v>
+      </c>
+      <c r="CF321" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG321" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH321" t="n">
+        <v>1379.469982137164</v>
+      </c>
+      <c r="CI321" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="CJ321" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK321" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL321" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM321" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN321" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO321" t="inlineStr">
+        <is>
+          <t>open_high_close_low, gap_chase_after_blowout</t>
+        </is>
+      </c>
+      <c r="CP321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C322" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D322" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="E322" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F322" t="n">
+        <v>3023462</v>
+      </c>
+      <c r="G322" t="n">
+        <v>48262510</v>
+      </c>
+      <c r="H322" t="n">
+        <v>6152</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>百一</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="n">
+        <v>-0.1339595260893116</v>
+      </c>
+      <c r="L322" t="n">
+        <v>-0.3697444086253703</v>
+      </c>
+      <c r="M322" t="n">
+        <v>0.2357848825360586</v>
+      </c>
+      <c r="N322" t="n">
+        <v>15.26765883922394</v>
+      </c>
+      <c r="O322" t="n">
+        <v>15.49222427482069</v>
+      </c>
+      <c r="P322" t="n">
+        <v>14.41042476432307</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>54.76117820797499</v>
+      </c>
+      <c r="R322" t="n">
+        <v>17.34609256085886</v>
+      </c>
+      <c r="S322" t="n">
+        <v>0.9538316532321832</v>
+      </c>
+      <c r="T322" t="n">
+        <v>1980976.2</v>
+      </c>
+      <c r="U322" t="n">
+        <v>29490281.3</v>
+      </c>
+      <c r="V322" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="W322" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X322" t="n">
+        <v>0.8051605304088681</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>-0.5468639199468609</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>0.0878378378378379</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>0.0454545454545454</v>
+      </c>
+      <c r="AB322" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="AC322" t="n">
+        <v>0.5772398708428081</v>
+      </c>
+      <c r="AD322" t="n">
+        <v>16.36660177965532</v>
+      </c>
+      <c r="AE322" t="n">
+        <v>14.62750000000001</v>
+      </c>
+      <c r="AF322" t="n">
+        <v>12.88839822034469</v>
+      </c>
+      <c r="AG322" t="n">
+        <v>0.9233507254221311</v>
+      </c>
+      <c r="AH322" t="n">
+        <v>0.2377852373481884</v>
+      </c>
+      <c r="AI322" t="n">
+        <v>82.22222222222229</v>
+      </c>
+      <c r="AJ322" t="n">
+        <v>60.83788706739566</v>
+      </c>
+      <c r="AK322" t="n">
+        <v>47873710</v>
+      </c>
+      <c r="AL322" t="n">
+        <v>41977116.9</v>
+      </c>
+      <c r="AM322" t="n">
+        <v>-13.11475409836061</v>
+      </c>
+      <c r="AN322" t="n">
+        <v>112.0473022912048</v>
+      </c>
+      <c r="AO322" t="n">
+        <v>70.20513570768196</v>
+      </c>
+      <c r="AP322" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AQ322" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="AR322" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS322" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT322" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU322" t="n">
+        <v>1156000</v>
+      </c>
+      <c r="AV322" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ322" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA322" t="n">
+        <v>0.0612258265217871</v>
+      </c>
+      <c r="BB322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD322" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE322" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF322" t="n">
+        <v>1.526248523329054</v>
+      </c>
+      <c r="BG322" t="b">
+        <v>1</v>
+      </c>
+      <c r="BH322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ322" t="b">
+        <v>1</v>
+      </c>
+      <c r="BK322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM322" t="b">
+        <v>1</v>
+      </c>
+      <c r="BN322" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP322" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT322" t="b">
+        <v>1</v>
+      </c>
+      <c r="BU322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV322" t="b">
+        <v>1</v>
+      </c>
+      <c r="BW322" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BY322" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ322" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA322" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB322" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC322" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD322" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE322" t="n">
+        <v>11</v>
+      </c>
+      <c r="CF322" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG322" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH322" t="n">
+        <v>1238.731160446328</v>
+      </c>
+      <c r="CI322" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="CJ322" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK322" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL322" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM322" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN322" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+        </is>
+      </c>
+      <c r="CO322" t="inlineStr"/>
+      <c r="CP322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="C323" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="D323" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E323" t="n">
+        <v>34</v>
+      </c>
+      <c r="F323" t="n">
+        <v>2552418</v>
+      </c>
+      <c r="G323" t="n">
+        <v>88636589</v>
+      </c>
+      <c r="H323" t="n">
+        <v>6141</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>柏承</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="n">
+        <v>1.506118809469907</v>
+      </c>
+      <c r="L323" t="n">
+        <v>1.694593161082123</v>
+      </c>
+      <c r="M323" t="n">
+        <v>-0.1884743516122164</v>
+      </c>
+      <c r="N323" t="n">
+        <v>31.69556206832608</v>
+      </c>
+      <c r="O323" t="n">
+        <v>26.37239465464055</v>
+      </c>
+      <c r="P323" t="n">
+        <v>21.46076682572066</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>58.07284773399088</v>
+      </c>
+      <c r="R323" t="n">
+        <v>23.69783336511352</v>
+      </c>
+      <c r="S323" t="n">
+        <v>2.92194227705927</v>
+      </c>
+      <c r="T323" t="n">
+        <v>2182305.25</v>
+      </c>
+      <c r="U323" t="n">
+        <v>70386943.25</v>
+      </c>
+      <c r="V323" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="W323" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="X323" t="n">
+        <v>-0.0563658261712555</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>1.528595705823293</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>0.2035398230088496</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB323" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC323" t="n">
+        <v>1.588334189142588</v>
+      </c>
+      <c r="AD323" t="n">
+        <v>38.00060992991237</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>32.49249999999999</v>
+      </c>
+      <c r="AF323" t="n">
+        <v>26.98439007008761</v>
+      </c>
+      <c r="AG323" t="n">
+        <v>0.6368436740716963</v>
+      </c>
+      <c r="AH323" t="n">
+        <v>0.3390388508063325</v>
+      </c>
+      <c r="AI323" t="n">
+        <v>76.678445229682</v>
+      </c>
+      <c r="AJ323" t="n">
+        <v>77.85630153121262</v>
+      </c>
+      <c r="AK323" t="n">
+        <v>91575515</v>
+      </c>
+      <c r="AL323" t="n">
+        <v>80622123.5</v>
+      </c>
+      <c r="AM323" t="n">
+        <v>-31.54574132492113</v>
+      </c>
+      <c r="AN323" t="n">
+        <v>59.85149451381008</v>
+      </c>
+      <c r="AO323" t="n">
+        <v>67.96079872921476</v>
+      </c>
+      <c r="AP323" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="AQ323" t="n">
+        <v>19.525</v>
+      </c>
+      <c r="AR323" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS323" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT323" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU323" t="n">
+        <v>-38000</v>
+      </c>
+      <c r="AV323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY323" t="n">
+        <v>-17000</v>
+      </c>
+      <c r="AZ323" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA323" t="n">
+        <v>0.1769278116927988</v>
+      </c>
+      <c r="BB323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD323" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE323" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF323" t="n">
+        <v>1.169597149619651</v>
+      </c>
+      <c r="BG323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH323" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI323" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL323" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN323" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP323" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV323" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW323" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX323" t="b">
+        <v>1</v>
+      </c>
+      <c r="BY323" t="b">
+        <v>1</v>
+      </c>
+      <c r="BZ323" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA323" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB323" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC323" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD323" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE323" t="n">
+        <v>10</v>
+      </c>
+      <c r="CF323" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG323" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH323" t="n">
+        <v>1123.08658603059</v>
+      </c>
+      <c r="CI323" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="CJ323" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK323" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL323" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM323" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN323" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+      <c r="CO323" t="inlineStr">
+        <is>
+          <t>long_upper_shadow</t>
+        </is>
+      </c>
+      <c r="CP323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="C324" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="D324" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="E324" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="F324" t="n">
+        <v>789615</v>
+      </c>
+      <c r="G324" t="n">
+        <v>6385992</v>
+      </c>
+      <c r="H324" t="n">
+        <v>6142</v>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>友勁</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr"/>
+      <c r="K324" t="n">
+        <v>-0.3419545814102331</v>
+      </c>
+      <c r="L324" t="n">
+        <v>-0.313276670071086</v>
+      </c>
+      <c r="M324" t="n">
+        <v>-0.0286779113391471</v>
+      </c>
+      <c r="N324" t="n">
+        <v>8.468734786502067</v>
+      </c>
+      <c r="O324" t="n">
+        <v>9.028232226892053</v>
+      </c>
+      <c r="P324" t="n">
+        <v>9.290677175883506</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>39.28306311877238</v>
+      </c>
+      <c r="R324" t="n">
+        <v>26.04668157539799</v>
+      </c>
+      <c r="S324" t="n">
+        <v>0.2641587543361338</v>
+      </c>
+      <c r="T324" t="n">
+        <v>694833.05</v>
+      </c>
+      <c r="U324" t="n">
+        <v>5942937.5</v>
+      </c>
+      <c r="V324" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="W324" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="X324" t="n">
+        <v>-0.774489617107783</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>-0.3481280524828202</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>0.0273972602739727</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>0.0299625468164794</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>0.8800372845791482</v>
+      </c>
+      <c r="AD324" t="n">
+        <v>9.36738908135152</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>8.533500000000027</v>
+      </c>
+      <c r="AF324" t="n">
+        <v>7.699610918648533</v>
+      </c>
+      <c r="AG324" t="n">
+        <v>0.3300133636834799</v>
+      </c>
+      <c r="AH324" t="n">
+        <v>0.1954389362750316</v>
+      </c>
+      <c r="AI324" t="n">
+        <v>46.6019417475728</v>
+      </c>
+      <c r="AJ324" t="n">
+        <v>24.11651858181722</v>
+      </c>
+      <c r="AK324" t="n">
+        <v>-3647950</v>
+      </c>
+      <c r="AL324" t="n">
+        <v>-551704.35</v>
+      </c>
+      <c r="AM324" t="n">
+        <v>-65.71428571428569</v>
+      </c>
+      <c r="AN324" t="n">
+        <v>-71.80779267524503</v>
+      </c>
+      <c r="AO324" t="n">
+        <v>26.63548898025203</v>
+      </c>
+      <c r="AP324" t="n">
+        <v>9.637499999999999</v>
+      </c>
+      <c r="AQ324" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="AR324" t="n">
+        <v>83262.20116666671</v>
+      </c>
+      <c r="AS324" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT324" t="n">
+        <v>0.0266120113160508</v>
+      </c>
+      <c r="AU324" t="n">
+        <v>258000</v>
+      </c>
+      <c r="AV324" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ324" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA324" t="n">
+        <v>0.0007852489579218</v>
+      </c>
+      <c r="BB324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF324" t="n">
+        <v>1.136409674237574</v>
+      </c>
+      <c r="BG324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI324" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK324" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM324" t="b">
+        <v>1</v>
+      </c>
+      <c r="BN324" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BR324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BS324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BX324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BY324" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ324" t="b">
+        <v>0</v>
+      </c>
+      <c r="CA324" t="b">
+        <v>0</v>
+      </c>
+      <c r="CB324" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC324" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CD324" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE324" t="n">
+        <v>5</v>
+      </c>
+      <c r="CF324" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG324" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH324" t="n">
+        <v>592.4893032135659</v>
+      </c>
+      <c r="CI324" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="CJ324" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK324" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL324" t="b">
+        <v>0</v>
+      </c>
+      <c r="CM324" t="b">
+        <v>1</v>
+      </c>
+      <c r="CN324" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+      <c r="CO324" t="inlineStr"/>
+      <c r="CP324" t="inlineStr">
+        <is>
+          <t>close_below_ema20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
